--- a/PAMF_DIG F2 - monthly2026-07-17.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-17.xlsx
@@ -3407,7 +3407,7 @@
         <v>0.09</v>
       </c>
       <c r="N41" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>0.09</v>
       </c>
       <c r="N176" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>0.09</v>
       </c>
       <c r="N244" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O244" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>0.09</v>
       </c>
       <c r="N245" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>0.09</v>
       </c>
       <c r="N291" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O291" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-17.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-17.xlsx
@@ -8298,7 +8298,7 @@
         <v>0.09</v>
       </c>
       <c r="N108" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>0.09</v>
       </c>
       <c r="N109" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>0.09</v>
       </c>
       <c r="N138" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>0.09</v>
       </c>
       <c r="N155" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>0.09</v>
       </c>
       <c r="N181" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>0.09</v>
       </c>
       <c r="N209" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>0.09</v>
       </c>
       <c r="N219" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>0.09</v>
       </c>
       <c r="N229" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>0.09</v>
       </c>
       <c r="N240" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>0.09</v>
       </c>
       <c r="N304" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O304" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>0.09</v>
       </c>
       <c r="N311" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O311" t="inlineStr">
         <is>
